--- a/branches/fix-extension-profile-pins/StructureDefinition-mii-lm-labor.xlsx
+++ b/branches/fix-extension-profile-pins/StructureDefinition-mii-lm-labor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:33:22+00:00</t>
+    <t>2026-09-02T14:48:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
